--- a/assessment_training_forms/003_pre_training_evaluation_for_safety_compliance--assessment_training_forms.xlsx
+++ b/assessment_training_forms/003_pre_training_evaluation_for_safety_compliance--assessment_training_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'safety'}</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Safety'}</t>
+          <t>Safety</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'2-5'}</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': '2-5'}</t>
+          <t>2-5</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'5+'}</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '5+'}</t>
+          <t>5+</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'no_opinion'}</t>
+          <t>no_opinion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'No Opinion'}</t>
+          <t>No Opinion</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'no_opinion'}</t>
+          <t>no_opinion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'No Opinion'}</t>
+          <t>No Opinion</t>
         </is>
       </c>
     </row>
